--- a/Data_clean/MCAS/Estados_US/Edos_USA_2019/MONTANA_2019.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2019/MONTANA_2019.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C9">
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -509,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Valle de Zaragoza</t>
+          <t>Valle De Zaragoza</t>
         </is>
       </c>
       <c r="C11">
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -568,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total</t>
@@ -628,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Total</t>
@@ -643,12 +703,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C20">
@@ -659,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C21">
@@ -672,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Ozumba</t>
@@ -685,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -698,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -729,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -742,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -755,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -768,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
@@ -788,7 +888,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C30">
@@ -799,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C31">
@@ -812,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -825,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -845,7 +960,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tezontepec de Aldama</t>
+          <t>Tezontepec De Aldama</t>
         </is>
       </c>
       <c r="C34">
@@ -856,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Total</t>
@@ -887,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -900,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cuautitlán de García Barragán</t>
+          <t>Cuautitlán De García Barragán</t>
         </is>
       </c>
       <c r="C38">
@@ -913,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -926,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -939,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -952,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C42">
@@ -965,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Villa Corona</t>
@@ -978,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -991,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1022,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -1035,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -1048,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -1061,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1092,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1105,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1136,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1167,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -1180,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1211,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1242,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -1255,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>San Nicolás Tolentino</t>
@@ -1268,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1299,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1330,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Yécora</t>
@@ -1343,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1374,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1405,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1425,7 +1680,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Amatlán de los Reyes</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C74">
@@ -1436,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -1449,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Mecayapan</t>
@@ -1462,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -1475,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1506,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Miguel Auza</t>
@@ -1519,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1542,41 +1827,6 @@
       </c>
       <c r="D82">
         <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 800,811</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Abril de 2020</t>
-        </is>
       </c>
     </row>
   </sheetData>
